--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/PbcPrdAccountSub.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/PbcPrdAccountSub.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18420" windowHeight="5860"/>
+    <workbookView xWindow="0" yWindow="2715" windowWidth="15675" windowHeight="5505"/>
   </bookViews>
   <sheets>
     <sheet name="资产池基本信息" sheetId="5" r:id="rId1"/>
     <sheet name="填写说明" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>数据状态</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -40,6 +39,9 @@
     <t>反馈状态</t>
   </si>
   <si>
+    <t>发起机构代码</t>
+  </si>
+  <si>
     <t>资产池名称</t>
   </si>
   <si>
@@ -52,14 +54,6 @@
   <si>
     <t>反馈资产池代码</t>
     <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>内部产品代码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>发起机构代码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -193,7 +187,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -235,7 +229,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -270,7 +264,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -479,8 +473,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" style="4"/>
     <col min="2" max="2" width="20" style="4" customWidth="1"/>
@@ -488,13 +482,13 @@
     <col min="4" max="5" width="20" style="4" customWidth="1"/>
     <col min="6" max="6" width="9" style="4"/>
     <col min="7" max="7" width="13" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.26953125" style="4" customWidth="1"/>
-    <col min="9" max="10" width="16.08984375" style="4" customWidth="1"/>
-    <col min="11" max="11" width="11" style="4" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.08984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.25" style="4" customWidth="1"/>
+    <col min="9" max="9" width="16.125" style="4" customWidth="1"/>
+    <col min="10" max="10" width="11" style="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.125" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -513,23 +507,20 @@
       <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
-        <v>8</v>
+      <c r="G1" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="6" t="s">
-        <v>11</v>
+      <c r="J1" s="7" t="s">
+        <v>7</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="L1" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -542,547 +533,547 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A179"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="31.90625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="31.875" style="2" customWidth="1"/>
     <col min="2" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A1" s="1"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A2" s="3"/>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A3" s="3"/>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A4" s="3"/>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A5" s="3"/>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A6" s="3"/>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A7" s="3"/>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A8" s="3"/>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A9" s="3"/>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A10" s="3"/>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A11" s="3"/>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A12" s="3"/>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A13" s="3"/>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A14" s="3"/>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A15" s="3"/>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A16" s="3"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A17"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A18"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A19"/>
     </row>
-    <row r="20" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A20"/>
     </row>
-    <row r="21" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A21"/>
     </row>
-    <row r="22" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A22"/>
     </row>
-    <row r="23" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A23"/>
     </row>
-    <row r="24" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A24"/>
     </row>
-    <row r="25" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A25"/>
     </row>
-    <row r="26" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A26"/>
     </row>
-    <row r="27" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A27"/>
     </row>
-    <row r="28" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A28"/>
     </row>
-    <row r="29" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A29"/>
     </row>
-    <row r="30" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A30"/>
     </row>
-    <row r="31" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A31"/>
     </row>
-    <row r="32" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A32"/>
     </row>
-    <row r="33" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A33"/>
     </row>
-    <row r="34" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A34"/>
     </row>
-    <row r="35" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A35"/>
     </row>
-    <row r="36" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A36"/>
     </row>
-    <row r="37" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A37"/>
     </row>
-    <row r="38" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A38"/>
     </row>
-    <row r="39" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A39"/>
     </row>
-    <row r="40" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A40"/>
     </row>
-    <row r="41" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A41"/>
     </row>
-    <row r="42" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A42"/>
     </row>
-    <row r="43" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A43"/>
     </row>
-    <row r="44" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A44"/>
     </row>
-    <row r="45" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A45"/>
     </row>
-    <row r="46" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A46"/>
     </row>
-    <row r="47" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A47"/>
     </row>
-    <row r="48" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A48"/>
     </row>
-    <row r="49" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A49"/>
     </row>
-    <row r="50" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A50"/>
     </row>
-    <row r="51" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A51"/>
     </row>
-    <row r="52" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A52"/>
     </row>
-    <row r="53" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A53"/>
     </row>
-    <row r="54" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A54"/>
     </row>
-    <row r="55" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A55"/>
     </row>
-    <row r="56" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A56"/>
     </row>
-    <row r="57" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A57"/>
     </row>
-    <row r="58" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A58"/>
     </row>
-    <row r="59" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A59"/>
     </row>
-    <row r="60" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A60"/>
     </row>
-    <row r="61" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A61"/>
     </row>
-    <row r="62" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A62"/>
     </row>
-    <row r="63" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A63"/>
     </row>
-    <row r="64" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A64"/>
     </row>
-    <row r="65" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A65"/>
     </row>
-    <row r="66" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A66"/>
     </row>
-    <row r="67" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A67"/>
     </row>
-    <row r="68" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A68"/>
     </row>
-    <row r="69" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A69"/>
     </row>
-    <row r="70" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A70"/>
     </row>
-    <row r="71" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A71"/>
     </row>
-    <row r="72" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A72"/>
     </row>
-    <row r="73" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A73"/>
     </row>
-    <row r="74" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A74"/>
     </row>
-    <row r="75" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A75"/>
     </row>
-    <row r="76" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A76"/>
     </row>
-    <row r="77" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A77"/>
     </row>
-    <row r="78" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A78"/>
     </row>
-    <row r="79" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A79"/>
     </row>
-    <row r="80" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A80"/>
     </row>
-    <row r="81" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A81"/>
     </row>
-    <row r="82" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A82"/>
     </row>
-    <row r="83" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A83"/>
     </row>
-    <row r="84" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A84"/>
     </row>
-    <row r="85" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A85"/>
     </row>
-    <row r="86" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A86"/>
     </row>
-    <row r="87" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A87"/>
     </row>
-    <row r="88" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A88"/>
     </row>
-    <row r="89" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A89"/>
     </row>
-    <row r="90" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A90"/>
     </row>
-    <row r="91" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A91"/>
     </row>
-    <row r="92" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A92"/>
     </row>
-    <row r="93" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A93"/>
     </row>
-    <row r="94" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A94"/>
     </row>
-    <row r="95" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A95"/>
     </row>
-    <row r="96" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A96"/>
     </row>
-    <row r="97" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A97"/>
     </row>
-    <row r="98" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A98"/>
     </row>
-    <row r="99" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A99"/>
     </row>
-    <row r="100" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A100"/>
     </row>
-    <row r="101" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A101"/>
     </row>
-    <row r="102" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A102"/>
     </row>
-    <row r="103" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A103"/>
     </row>
-    <row r="104" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A104"/>
     </row>
-    <row r="105" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A105"/>
     </row>
-    <row r="106" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A106"/>
     </row>
-    <row r="107" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A107"/>
     </row>
-    <row r="108" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A108"/>
     </row>
-    <row r="109" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A109"/>
     </row>
-    <row r="110" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A110"/>
     </row>
-    <row r="111" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A111"/>
     </row>
-    <row r="112" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A112"/>
     </row>
-    <row r="113" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A113"/>
     </row>
-    <row r="114" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A114"/>
     </row>
-    <row r="115" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A115"/>
     </row>
-    <row r="116" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A116"/>
     </row>
-    <row r="117" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A117"/>
     </row>
-    <row r="118" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A118"/>
     </row>
-    <row r="119" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A119"/>
     </row>
-    <row r="120" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A120"/>
     </row>
-    <row r="121" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A121"/>
     </row>
-    <row r="122" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A122"/>
     </row>
-    <row r="123" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A123"/>
     </row>
-    <row r="124" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A124"/>
     </row>
-    <row r="125" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A125"/>
     </row>
-    <row r="126" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A126"/>
     </row>
-    <row r="127" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A127"/>
     </row>
-    <row r="128" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A128"/>
     </row>
-    <row r="129" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A129"/>
     </row>
-    <row r="130" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A130"/>
     </row>
-    <row r="131" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A131"/>
     </row>
-    <row r="132" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A132"/>
     </row>
-    <row r="133" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A133"/>
     </row>
-    <row r="134" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A134"/>
     </row>
-    <row r="135" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A135"/>
     </row>
-    <row r="136" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A136"/>
     </row>
-    <row r="137" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A137"/>
     </row>
-    <row r="138" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A138"/>
     </row>
-    <row r="139" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A139"/>
     </row>
-    <row r="140" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A140"/>
     </row>
-    <row r="141" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A141"/>
     </row>
-    <row r="142" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A142"/>
     </row>
-    <row r="143" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A143"/>
     </row>
-    <row r="144" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A144"/>
     </row>
-    <row r="145" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A145"/>
     </row>
-    <row r="146" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A146"/>
     </row>
-    <row r="147" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A147"/>
     </row>
-    <row r="148" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A148"/>
     </row>
-    <row r="149" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A149"/>
     </row>
-    <row r="150" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A150"/>
     </row>
-    <row r="151" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A151"/>
     </row>
-    <row r="152" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A152"/>
     </row>
-    <row r="153" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A153"/>
     </row>
-    <row r="154" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A154"/>
     </row>
-    <row r="155" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A155"/>
     </row>
-    <row r="156" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A156"/>
     </row>
-    <row r="157" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A157"/>
     </row>
-    <row r="158" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A158"/>
     </row>
-    <row r="159" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A159"/>
     </row>
-    <row r="160" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A160"/>
     </row>
-    <row r="161" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A161"/>
     </row>
-    <row r="162" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A162"/>
     </row>
-    <row r="163" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A163"/>
     </row>
-    <row r="164" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A164"/>
     </row>
-    <row r="165" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A165"/>
     </row>
-    <row r="166" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A166"/>
     </row>
-    <row r="167" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A167"/>
     </row>
-    <row r="168" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A168"/>
     </row>
-    <row r="169" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A169"/>
     </row>
-    <row r="170" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A170"/>
     </row>
-    <row r="171" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A171"/>
     </row>
-    <row r="172" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A172"/>
     </row>
-    <row r="173" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A173"/>
     </row>
-    <row r="174" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A174"/>
     </row>
-    <row r="175" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A175"/>
     </row>
-    <row r="176" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A176"/>
     </row>
-    <row r="177" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A177"/>
     </row>
-    <row r="178" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A178"/>
     </row>
-    <row r="179" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A179"/>
     </row>
   </sheetData>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/PbcPrdAccountSub.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/PbcPrdAccountSub.xlsx
@@ -1,39 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2715" windowWidth="15675" windowHeight="5505"/>
+    <workbookView windowWidth="19815" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="资产池基本信息" sheetId="5" r:id="rId1"/>
     <sheet name="填写说明" sheetId="4" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <si>
     <t>数据状态</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>数据日期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>报送状态</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>报送日期</t>
   </si>
   <si>
     <t>报送截止日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>反馈状态</t>
@@ -42,71 +38,213 @@
     <t>发起机构代码</t>
   </si>
   <si>
+    <t>资产池代码</t>
+  </si>
+  <si>
+    <t>反馈资产池代码</t>
+  </si>
+  <si>
+    <t>内部产品代码</t>
+  </si>
+  <si>
     <t>资产池名称</t>
   </si>
   <si>
     <t>资产池起始日期</t>
   </si>
-  <si>
-    <t>资产池代码</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>反馈资产池代码</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF373737"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF373737"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -119,8 +257,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -130,57 +454,343 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <colors>
     <mruColors>
-      <color rgb="FF00CCFF"/>
-      <color rgb="FF3399FF"/>
+      <color rgb="0000CCFF"/>
+      <color rgb="003399FF"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -467,618 +1077,625 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:M1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="9" style="4"/>
-    <col min="2" max="2" width="20" style="4" customWidth="1"/>
-    <col min="3" max="3" width="9" style="4"/>
-    <col min="4" max="5" width="20" style="4" customWidth="1"/>
-    <col min="6" max="6" width="9" style="4"/>
-    <col min="7" max="7" width="13" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="4" customWidth="1"/>
-    <col min="9" max="9" width="16.125" style="4" customWidth="1"/>
-    <col min="10" max="10" width="11" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9" style="5"/>
+    <col min="2" max="2" width="20" style="5" customWidth="1"/>
+    <col min="3" max="3" width="9" style="5"/>
+    <col min="4" max="5" width="20" style="5" customWidth="1"/>
+    <col min="6" max="6" width="9" style="5"/>
+    <col min="7" max="7" width="13" style="5" customWidth="1"/>
+    <col min="8" max="8" width="16.25" style="5" customWidth="1"/>
+    <col min="9" max="11" width="16.125" style="5" customWidth="1"/>
+    <col min="12" max="12" width="11" style="5" customWidth="1"/>
+    <col min="13" max="13" width="15.125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="5" t="s">
+    <row r="1" s="4" customFormat="1" spans="1:13">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="K1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="7" t="s">
-        <v>7</v>
+      <c r="M1" s="8" t="s">
+        <v>11</v>
       </c>
-      <c r="K1" s="7" t="s">
-        <v>8</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:A179"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="31.875" style="2" customWidth="1"/>
-    <col min="2" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="31.875" style="1" customWidth="1"/>
+    <col min="2" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A1" s="1"/>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:1">
+      <c r="A1" s="2"/>
+    </row>
+    <row r="2" spans="1:1">
       <c r="A2" s="3"/>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:1">
       <c r="A3" s="3"/>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:1">
       <c r="A4" s="3"/>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:1">
       <c r="A5" s="3"/>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:1">
       <c r="A6" s="3"/>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:1">
       <c r="A7" s="3"/>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:1">
       <c r="A8" s="3"/>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:1">
       <c r="A9" s="3"/>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:1">
       <c r="A10" s="3"/>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:1">
       <c r="A11" s="3"/>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:1">
       <c r="A12" s="3"/>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:1">
       <c r="A13" s="3"/>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:1">
       <c r="A14" s="3"/>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:1">
       <c r="A15" s="3"/>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:1">
       <c r="A16" s="3"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:1">
       <c r="A17"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:1">
       <c r="A18"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:1">
       <c r="A19"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:1">
       <c r="A20"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:1">
       <c r="A21"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:1">
       <c r="A22"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:1">
       <c r="A23"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:1">
       <c r="A24"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:1">
       <c r="A25"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:1">
       <c r="A26"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:1">
       <c r="A27"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:1">
       <c r="A28"/>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:1">
       <c r="A29"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:1">
       <c r="A30"/>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:1">
       <c r="A31"/>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:1">
       <c r="A32"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:1">
       <c r="A33"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:1">
       <c r="A34"/>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:1">
       <c r="A35"/>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:1">
       <c r="A36"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:1">
       <c r="A37"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:1">
       <c r="A38"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:1">
       <c r="A39"/>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:1">
       <c r="A40"/>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:1">
       <c r="A41"/>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:1">
       <c r="A42"/>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:1">
       <c r="A43"/>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:1">
       <c r="A44"/>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:1">
       <c r="A45"/>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:1">
       <c r="A46"/>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:1">
       <c r="A47"/>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:1">
       <c r="A48"/>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:1">
       <c r="A49"/>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:1">
       <c r="A50"/>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:1">
       <c r="A51"/>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:1">
       <c r="A52"/>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:1">
       <c r="A53"/>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:1">
       <c r="A54"/>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:1">
       <c r="A55"/>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:1">
       <c r="A56"/>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:1">
       <c r="A57"/>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:1">
       <c r="A58"/>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:1">
       <c r="A59"/>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:1">
       <c r="A60"/>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:1">
       <c r="A61"/>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:1">
       <c r="A62"/>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:1">
       <c r="A63"/>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:1">
       <c r="A64"/>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:1">
       <c r="A65"/>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:1">
       <c r="A66"/>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:1">
       <c r="A67"/>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:1">
       <c r="A68"/>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:1">
       <c r="A69"/>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:1">
       <c r="A70"/>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:1">
       <c r="A71"/>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:1">
       <c r="A72"/>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:1">
       <c r="A73"/>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:1">
       <c r="A74"/>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:1">
       <c r="A75"/>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:1">
       <c r="A76"/>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:1">
       <c r="A77"/>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:1">
       <c r="A78"/>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:1">
       <c r="A79"/>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:1">
       <c r="A80"/>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:1">
       <c r="A81"/>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:1">
       <c r="A82"/>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:1">
       <c r="A83"/>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:1">
       <c r="A84"/>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:1">
       <c r="A85"/>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:1">
       <c r="A86"/>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:1">
       <c r="A87"/>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:1">
       <c r="A88"/>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:1">
       <c r="A89"/>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:1">
       <c r="A90"/>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:1">
       <c r="A91"/>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:1">
       <c r="A92"/>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:1">
       <c r="A93"/>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:1">
       <c r="A94"/>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:1">
       <c r="A95"/>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:1">
       <c r="A96"/>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:1">
       <c r="A97"/>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:1">
       <c r="A98"/>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:1">
       <c r="A99"/>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:1">
       <c r="A100"/>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:1">
       <c r="A101"/>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:1">
       <c r="A102"/>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:1">
       <c r="A103"/>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:1">
       <c r="A104"/>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:1">
       <c r="A105"/>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:1">
       <c r="A106"/>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:1">
       <c r="A107"/>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:1">
       <c r="A108"/>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:1">
       <c r="A109"/>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:1">
       <c r="A110"/>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:1">
       <c r="A111"/>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:1">
       <c r="A112"/>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:1">
       <c r="A113"/>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:1">
       <c r="A114"/>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:1">
       <c r="A115"/>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:1">
       <c r="A116"/>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:1">
       <c r="A117"/>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:1">
       <c r="A118"/>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:1">
       <c r="A119"/>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:1">
       <c r="A120"/>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:1">
       <c r="A121"/>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:1">
       <c r="A122"/>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:1">
       <c r="A123"/>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:1">
       <c r="A124"/>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:1">
       <c r="A125"/>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:1">
       <c r="A126"/>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:1">
       <c r="A127"/>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:1">
       <c r="A128"/>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:1">
       <c r="A129"/>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:1">
       <c r="A130"/>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:1">
       <c r="A131"/>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:1">
       <c r="A132"/>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:1">
       <c r="A133"/>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:1">
       <c r="A134"/>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:1">
       <c r="A135"/>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:1">
       <c r="A136"/>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:1">
       <c r="A137"/>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:1">
       <c r="A138"/>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:1">
       <c r="A139"/>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:1">
       <c r="A140"/>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:1">
       <c r="A141"/>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:1">
       <c r="A142"/>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:1">
       <c r="A143"/>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:1">
       <c r="A144"/>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:1">
       <c r="A145"/>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:1">
       <c r="A146"/>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:1">
       <c r="A147"/>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:1">
       <c r="A148"/>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:1">
       <c r="A149"/>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:1">
       <c r="A150"/>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:1">
       <c r="A151"/>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:1">
       <c r="A152"/>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:1">
       <c r="A153"/>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:1">
       <c r="A154"/>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:1">
       <c r="A155"/>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:1">
       <c r="A156"/>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:1">
       <c r="A157"/>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:1">
       <c r="A158"/>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:1">
       <c r="A159"/>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="160" spans="1:1">
       <c r="A160"/>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:1">
       <c r="A161"/>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:1">
       <c r="A162"/>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="163" spans="1:1">
       <c r="A163"/>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="164" spans="1:1">
       <c r="A164"/>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:1">
       <c r="A165"/>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:1">
       <c r="A166"/>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:1">
       <c r="A167"/>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="168" spans="1:1">
       <c r="A168"/>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:1">
       <c r="A169"/>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:1">
       <c r="A170"/>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="171" spans="1:1">
       <c r="A171"/>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="172" spans="1:1">
       <c r="A172"/>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="173" spans="1:1">
       <c r="A173"/>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:1">
       <c r="A174"/>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="175" spans="1:1">
       <c r="A175"/>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:1">
       <c r="A176"/>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:1">
       <c r="A177"/>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:1">
       <c r="A178"/>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:1">
       <c r="A179"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" copies="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/PbcPrdAccountSub.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/PbcPrdAccountSub.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19815" windowHeight="8010"/>
+    <workbookView windowWidth="19815" windowHeight="7860"/>
   </bookViews>
   <sheets>
     <sheet name="资产池基本信息" sheetId="5" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>数据状态</t>
   </si>
@@ -35,9 +35,6 @@
     <t>反馈状态</t>
   </si>
   <si>
-    <t>发起机构代码</t>
-  </si>
-  <si>
     <t>资产池代码</t>
   </si>
   <si>
@@ -45,6 +42,9 @@
   </si>
   <si>
     <t>内部产品代码</t>
+  </si>
+  <si>
+    <t>发起机构代码</t>
   </si>
   <si>
     <t>资产池名称</t>
@@ -58,12 +58,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -72,6 +72,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -79,23 +80,121 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF373737"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF373737"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -111,28 +210,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -140,105 +225,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -265,55 +251,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -325,37 +395,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -367,31 +407,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -403,43 +425,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -469,30 +455,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -507,32 +469,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -555,6 +496,51 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -568,157 +554,157 @@
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -1083,7 +1069,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
@@ -1091,14 +1077,13 @@
     <col min="3" max="3" width="9" style="5"/>
     <col min="4" max="5" width="20" style="5" customWidth="1"/>
     <col min="6" max="6" width="9" style="5"/>
-    <col min="7" max="7" width="13" style="5" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="5" customWidth="1"/>
-    <col min="9" max="11" width="16.125" style="5" customWidth="1"/>
-    <col min="12" max="12" width="11" style="5" customWidth="1"/>
-    <col min="13" max="13" width="15.125" style="5" customWidth="1"/>
+    <col min="7" max="7" width="16.25" style="5" customWidth="1"/>
+    <col min="8" max="10" width="16.125" style="5" customWidth="1"/>
+    <col min="11" max="11" width="11" style="5" customWidth="1"/>
+    <col min="12" max="12" width="15.125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="4" customFormat="1" spans="1:13">
+    <row r="1" s="4" customFormat="1" spans="1:12">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1117,7 +1102,7 @@
       <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="7" t="s">
@@ -1129,13 +1114,10 @@
       <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="7" t="s">
-        <v>6</v>
+      <c r="K1" s="8" t="s">
+        <v>10</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="8" t="s">
         <v>11</v>
       </c>
     </row>
